--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.31616862110714</v>
+        <v>6.22637740092991</v>
       </c>
       <c r="D2" t="n">
-        <v>38.43770527826003</v>
+        <v>6.246127107717256</v>
       </c>
       <c r="E2" t="n">
-        <v>15.4816587181873</v>
+        <v>2.515769541705437</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1817477611929</v>
+        <v>2.142034011193847</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.482151358284074</v>
+        <v>1.378349595721162</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1206212832563</v>
+        <v>1.319600958529149</v>
       </c>
       <c r="E3" t="n">
-        <v>15.4816587181873</v>
+        <v>2.515769541705437</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1817477611929</v>
+        <v>2.142034011193847</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.48499102500131</v>
+        <v>7.066311041562712</v>
       </c>
       <c r="D4" t="n">
-        <v>43.75239728444493</v>
+        <v>7.109764558722302</v>
       </c>
       <c r="E4" t="n">
-        <v>15.4816587181873</v>
+        <v>2.515769541705437</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1817477611929</v>
+        <v>2.142034011193847</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.86991898537684</v>
+        <v>4.691361835123736</v>
       </c>
       <c r="D5" t="n">
-        <v>32.3239918629195</v>
+        <v>5.252648677724419</v>
       </c>
       <c r="E5" t="n">
-        <v>15.4816587181873</v>
+        <v>2.515769541705437</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1817477611929</v>
+        <v>2.142034011193847</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.36699494836771</v>
+        <v>8.834636679109753</v>
       </c>
       <c r="D6" t="n">
-        <v>18.10398113746696</v>
+        <v>2.94189693483838</v>
       </c>
       <c r="E6" t="n">
-        <v>15.4816587181873</v>
+        <v>2.515769541705437</v>
       </c>
       <c r="F6" t="n">
-        <v>13.1817477611929</v>
+        <v>2.142034011193847</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
